--- a/liste_etudiants.xlsx
+++ b/liste_etudiants.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Stephano\Documents\TRAVAIL\Photo-univ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AC385F-257D-426C-8C8E-A99DFAB988D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7525F581-BC53-4718-AAE0-7DEF33071314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11442" yWindow="0" windowWidth="11676" windowHeight="12318" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="1200" windowWidth="17280" windowHeight="8904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="919">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="921">
   <si>
     <t>nom</t>
   </si>
@@ -2782,6 +2782,12 @@
   </si>
   <si>
     <t>photo</t>
+  </si>
+  <si>
+    <t>Pas de photo</t>
+  </si>
+  <si>
+    <t>Photo OK</t>
   </si>
 </sst>
 </file>
@@ -3464,7 +3470,19 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{753D0848-A00E-455B-97D1-991CCD9E49CC}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3837,6 +3855,9 @@
       <c r="L2" s="38" t="s">
         <v>210</v>
       </c>
+      <c r="M2" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
@@ -3875,6 +3896,9 @@
       <c r="L3" s="38" t="s">
         <v>211</v>
       </c>
+      <c r="M3" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
@@ -3913,6 +3937,9 @@
       <c r="L4" s="38" t="s">
         <v>212</v>
       </c>
+      <c r="M4" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
@@ -3951,6 +3978,9 @@
       <c r="L5" s="38" t="s">
         <v>213</v>
       </c>
+      <c r="M5" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
@@ -3989,6 +4019,9 @@
       <c r="L6" s="38" t="s">
         <v>214</v>
       </c>
+      <c r="M6" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
@@ -4027,6 +4060,9 @@
       <c r="L7" s="38" t="s">
         <v>215</v>
       </c>
+      <c r="M7" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="4" t="s">
@@ -4065,6 +4101,9 @@
       <c r="L8" s="39" t="s">
         <v>216</v>
       </c>
+      <c r="M8" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6" t="s">
@@ -4101,6 +4140,9 @@
       <c r="L9" s="40" t="s">
         <v>217</v>
       </c>
+      <c r="M9" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6" t="s">
@@ -4139,6 +4181,9 @@
       <c r="L10" s="41" t="s">
         <v>218</v>
       </c>
+      <c r="M10" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="8" t="s">
@@ -4177,6 +4222,9 @@
       <c r="L11" s="42" t="s">
         <v>219</v>
       </c>
+      <c r="M11" t="s">
+        <v>919</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="8" t="s">
@@ -4215,6 +4263,9 @@
       <c r="L12" s="43" t="s">
         <v>220</v>
       </c>
+      <c r="M12" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="8" t="s">
@@ -4253,6 +4304,9 @@
       <c r="L13" s="44" t="s">
         <v>221</v>
       </c>
+      <c r="M13" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="8" t="s">
@@ -4291,6 +4345,9 @@
       <c r="L14" s="42" t="s">
         <v>222</v>
       </c>
+      <c r="M14" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6" t="s">
@@ -4329,6 +4386,9 @@
       <c r="L15" s="41" t="s">
         <v>223</v>
       </c>
+      <c r="M15" t="s">
+        <v>920</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="8" t="s">
@@ -4367,8 +4427,11 @@
       <c r="L16" s="44" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M16" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="8" t="s">
         <v>56</v>
       </c>
@@ -4405,8 +4468,11 @@
       <c r="L17" s="42" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M17" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="6" t="s">
         <v>59</v>
       </c>
@@ -4443,8 +4509,11 @@
       <c r="L18" s="41" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M18" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6" t="s">
         <v>62</v>
       </c>
@@ -4481,8 +4550,11 @@
       <c r="L19" s="41" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M19" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="6" t="s">
         <v>65</v>
       </c>
@@ -4519,8 +4591,11 @@
       <c r="L20" s="40" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M20" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="8" t="s">
         <v>68</v>
       </c>
@@ -4557,8 +4632,11 @@
       <c r="L21" s="44" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M21" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="6" t="s">
         <v>71</v>
       </c>
@@ -4595,8 +4673,11 @@
       <c r="L22" s="41" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M22" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="6" t="s">
         <v>74</v>
       </c>
@@ -4633,8 +4714,11 @@
       <c r="L23" s="40" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M23" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="6" t="s">
         <v>77</v>
       </c>
@@ -4671,8 +4755,11 @@
       <c r="L24" s="41" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M24" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="8" t="s">
         <v>80</v>
       </c>
@@ -4709,8 +4796,11 @@
       <c r="L25" s="42" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M25" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="6" t="s">
         <v>83</v>
       </c>
@@ -4747,8 +4837,11 @@
       <c r="L26" s="41" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M26" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="6" t="s">
         <v>86</v>
       </c>
@@ -4783,8 +4876,11 @@
       <c r="L27" s="41" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M27" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="6" t="s">
         <v>88</v>
       </c>
@@ -4821,8 +4917,11 @@
       <c r="L28" s="41" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M28" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="6" t="s">
         <v>91</v>
       </c>
@@ -4859,8 +4958,11 @@
       <c r="L29" s="41" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M29" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="6" t="s">
         <v>94</v>
       </c>
@@ -4897,8 +4999,11 @@
       <c r="L30" s="41" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M30" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="6" t="s">
         <v>97</v>
       </c>
@@ -4935,8 +5040,11 @@
       <c r="L31" s="45" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M31" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="8" t="s">
         <v>100</v>
       </c>
@@ -4973,8 +5081,11 @@
       <c r="L32" s="42" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M32" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="6" t="s">
         <v>103</v>
       </c>
@@ -5009,8 +5120,11 @@
       <c r="L33" s="40" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M33" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="6" t="s">
         <v>105</v>
       </c>
@@ -5045,8 +5159,11 @@
       <c r="L34" s="40" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M34" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="6" t="s">
         <v>107</v>
       </c>
@@ -5083,8 +5200,11 @@
       <c r="L35" s="41" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M35" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="8" t="s">
         <v>110</v>
       </c>
@@ -5121,8 +5241,11 @@
       <c r="L36" s="42" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M36" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="8" t="s">
         <v>113</v>
       </c>
@@ -5159,8 +5282,11 @@
       <c r="L37" s="42" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M37" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="8" t="s">
         <v>116</v>
       </c>
@@ -5197,8 +5323,11 @@
       <c r="L38" s="44" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M38" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="6" t="s">
         <v>119</v>
       </c>
@@ -5235,8 +5364,11 @@
       <c r="L39" s="40" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M39" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="6" t="s">
         <v>122</v>
       </c>
@@ -5271,8 +5403,11 @@
       <c r="L40" s="40" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M40" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="8" t="s">
         <v>124</v>
       </c>
@@ -5307,8 +5442,11 @@
       <c r="L41" s="42" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M41" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="6" t="s">
         <v>126</v>
       </c>
@@ -5343,8 +5481,11 @@
       <c r="L42" s="46" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M42" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="8" t="s">
         <v>128</v>
       </c>
@@ -5381,8 +5522,11 @@
       <c r="L43" s="44" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M43" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="6" t="s">
         <v>131</v>
       </c>
@@ -5419,8 +5563,11 @@
       <c r="L44" s="47" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M44" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="6" t="s">
         <v>134</v>
       </c>
@@ -5455,8 +5602,11 @@
       <c r="L45" s="48" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M45" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="8" t="s">
         <v>136</v>
       </c>
@@ -5491,8 +5641,11 @@
       <c r="L46" s="49" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M46" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="4" t="s">
         <v>255</v>
       </c>
@@ -5529,8 +5682,11 @@
       <c r="L47" s="107" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M47" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="4" t="s">
         <v>258</v>
       </c>
@@ -5567,8 +5723,11 @@
       <c r="L48" s="107" t="s">
         <v>745</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M48" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="4" t="s">
         <v>261</v>
       </c>
@@ -5605,8 +5764,11 @@
       <c r="L49" s="107" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M49" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="4" t="s">
         <v>264</v>
       </c>
@@ -5643,8 +5805,11 @@
       <c r="L50" s="107" t="s">
         <v>747</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M50" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="4" t="s">
         <v>267</v>
       </c>
@@ -5681,8 +5846,11 @@
       <c r="L51" s="107" t="s">
         <v>748</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M51" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="4" t="s">
         <v>270</v>
       </c>
@@ -5717,8 +5885,11 @@
       <c r="L52" s="107" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M52" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="4" t="s">
         <v>272</v>
       </c>
@@ -5755,8 +5926,11 @@
       <c r="L53" s="107" t="s">
         <v>750</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M53" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="4" t="s">
         <v>275</v>
       </c>
@@ -5793,8 +5967,11 @@
       <c r="L54" s="109" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M54" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="4" t="s">
         <v>278</v>
       </c>
@@ -5829,8 +6006,11 @@
       <c r="L55" s="109" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M55" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="4" t="s">
         <v>280</v>
       </c>
@@ -5867,8 +6047,11 @@
       <c r="L56" s="107" t="s">
         <v>753</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M56" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="4" t="s">
         <v>283</v>
       </c>
@@ -5905,8 +6088,11 @@
       <c r="L57" s="107" t="s">
         <v>754</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M57" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="4" t="s">
         <v>286</v>
       </c>
@@ -5943,8 +6129,11 @@
       <c r="L58" s="107" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M58" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="4" t="s">
         <v>289</v>
       </c>
@@ -5981,8 +6170,11 @@
       <c r="L59" s="107" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M59" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="8" t="s">
         <v>292</v>
       </c>
@@ -6019,8 +6211,11 @@
       <c r="L60" s="110" t="s">
         <v>757</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M60" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="8" t="s">
         <v>295</v>
       </c>
@@ -6055,8 +6250,11 @@
       <c r="L61" s="110" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M61" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="50" t="s">
         <v>297</v>
       </c>
@@ -6091,8 +6289,11 @@
       <c r="L62" s="110" t="s">
         <v>759</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M62" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="50" t="s">
         <v>299</v>
       </c>
@@ -6129,8 +6330,11 @@
       <c r="L63" s="110" t="s">
         <v>760</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M63" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="50" t="s">
         <v>302</v>
       </c>
@@ -6165,8 +6369,11 @@
       <c r="L64" s="110" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M64" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="50" t="s">
         <v>304</v>
       </c>
@@ -6203,8 +6410,11 @@
       <c r="L65" s="110" t="s">
         <v>762</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M65" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="8" t="s">
         <v>307</v>
       </c>
@@ -6241,8 +6451,11 @@
       <c r="L66" s="49" t="s">
         <v>763</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M66" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="8" t="s">
         <v>310</v>
       </c>
@@ -6277,8 +6490,11 @@
       <c r="L67" s="110" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M67" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="8" t="s">
         <v>312</v>
       </c>
@@ -6315,8 +6531,11 @@
       <c r="L68" s="110" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M68" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="8" t="s">
         <v>315</v>
       </c>
@@ -6353,8 +6572,11 @@
       <c r="L69" s="110" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M69" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="8" t="s">
         <v>318</v>
       </c>
@@ -6391,8 +6613,11 @@
       <c r="L70" s="110" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M70" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="8" t="s">
         <v>321</v>
       </c>
@@ -6429,8 +6654,11 @@
       <c r="L71" s="111" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M71" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="8" t="s">
         <v>324</v>
       </c>
@@ -6465,8 +6693,11 @@
         <v>209</v>
       </c>
       <c r="L72" s="110"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M72" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="8" t="s">
         <v>327</v>
       </c>
@@ -6503,8 +6734,11 @@
       <c r="L73" s="110" t="s">
         <v>769</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M73" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="8" t="s">
         <v>330</v>
       </c>
@@ -6541,8 +6775,11 @@
       <c r="L74" s="110" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M74" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="8" t="s">
         <v>333</v>
       </c>
@@ -6579,8 +6816,11 @@
       <c r="L75" s="110" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M75" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="8" t="s">
         <v>336</v>
       </c>
@@ -6617,8 +6857,11 @@
       <c r="L76" s="79" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M76" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="8" t="s">
         <v>339</v>
       </c>
@@ -6655,8 +6898,11 @@
       <c r="L77" s="110" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M77" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="8" t="s">
         <v>339</v>
       </c>
@@ -6693,8 +6939,11 @@
       <c r="L78" s="110" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M78" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="8" t="s">
         <v>344</v>
       </c>
@@ -6731,8 +6980,11 @@
       <c r="L79" s="110" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M79" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="8" t="s">
         <v>347</v>
       </c>
@@ -6769,8 +7021,11 @@
       <c r="L80" s="110" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M80" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="8" t="s">
         <v>350</v>
       </c>
@@ -6807,8 +7062,11 @@
       <c r="L81" s="110" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="82" spans="1:12" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="M81" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="8" t="s">
         <v>353</v>
       </c>
@@ -6845,8 +7103,11 @@
       <c r="L82" s="111" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M82" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="8" t="s">
         <v>356</v>
       </c>
@@ -6883,8 +7144,11 @@
       <c r="L83" s="110" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M83" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="8" t="s">
         <v>359</v>
       </c>
@@ -6921,8 +7185,11 @@
       <c r="L84" s="110" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M84" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="8" t="s">
         <v>362</v>
       </c>
@@ -6959,8 +7226,11 @@
       <c r="L85" s="110" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M85" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="8" t="s">
         <v>365</v>
       </c>
@@ -6997,8 +7267,11 @@
       <c r="L86" s="111" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M86" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="8" t="s">
         <v>368</v>
       </c>
@@ -7035,8 +7308,11 @@
       <c r="L87" s="110" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M87" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="8" t="s">
         <v>370</v>
       </c>
@@ -7071,8 +7347,11 @@
       <c r="L88" s="110" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M88" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="8" t="s">
         <v>372</v>
       </c>
@@ -7109,8 +7388,11 @@
       <c r="L89" s="110" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M89" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="8" t="s">
         <v>375</v>
       </c>
@@ -7147,8 +7429,11 @@
       <c r="L90" s="110" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M90" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="8" t="s">
         <v>378</v>
       </c>
@@ -7185,8 +7470,11 @@
       <c r="L91" s="110" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M91" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="8" t="s">
         <v>381</v>
       </c>
@@ -7223,8 +7511,11 @@
       <c r="L92" s="110" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M92" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="8" t="s">
         <v>384</v>
       </c>
@@ -7261,8 +7552,11 @@
       <c r="L93" s="110" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M93" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="8" t="s">
         <v>387</v>
       </c>
@@ -7299,8 +7593,11 @@
       <c r="L94" s="110" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M94" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="8" t="s">
         <v>390</v>
       </c>
@@ -7337,8 +7634,11 @@
       <c r="L95" s="110" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M95" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="8" t="s">
         <v>393</v>
       </c>
@@ -7375,8 +7675,11 @@
       <c r="L96" s="110" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M96" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="8" t="s">
         <v>396</v>
       </c>
@@ -7413,8 +7716,11 @@
       <c r="L97" s="110" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M97" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="8" t="s">
         <v>399</v>
       </c>
@@ -7451,8 +7757,11 @@
       <c r="L98" s="110" t="s">
         <v>794</v>
       </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M98" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="51" t="s">
         <v>402</v>
       </c>
@@ -7489,8 +7798,11 @@
       <c r="L99" s="113" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M99" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="8" t="s">
         <v>405</v>
       </c>
@@ -7527,8 +7839,11 @@
       <c r="L100" s="110" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M100" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="8" t="s">
         <v>408</v>
       </c>
@@ -7565,8 +7880,11 @@
       <c r="L101" s="110" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M101" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="8" t="s">
         <v>411</v>
       </c>
@@ -7603,8 +7921,11 @@
       <c r="L102" s="110" t="s">
         <v>798</v>
       </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M102" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="8" t="s">
         <v>414</v>
       </c>
@@ -7641,8 +7962,11 @@
       <c r="L103" s="110" t="s">
         <v>799</v>
       </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M103" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="8" t="s">
         <v>417</v>
       </c>
@@ -7679,8 +8003,11 @@
       <c r="L104" s="110" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M104" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="8" t="s">
         <v>420</v>
       </c>
@@ -7717,8 +8044,11 @@
       <c r="L105" s="110" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M105" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="8" t="s">
         <v>423</v>
       </c>
@@ -7755,8 +8085,11 @@
       <c r="L106" s="110" t="s">
         <v>802</v>
       </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M106" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="53" t="s">
         <v>426</v>
       </c>
@@ -7793,8 +8126,11 @@
       <c r="L107" s="115" t="s">
         <v>804</v>
       </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M107" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="4" t="s">
         <v>429</v>
       </c>
@@ -7831,8 +8167,11 @@
       <c r="L108" s="117" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M108" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="4" t="s">
         <v>432</v>
       </c>
@@ -7867,8 +8206,11 @@
       <c r="L109" s="117" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M109" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="4" t="s">
         <v>434</v>
       </c>
@@ -7905,8 +8247,11 @@
       <c r="L110" s="117" t="s">
         <v>807</v>
       </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M110" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="4" t="s">
         <v>437</v>
       </c>
@@ -7941,8 +8286,11 @@
       <c r="L111" s="117" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M111" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="4" t="s">
         <v>439</v>
       </c>
@@ -7979,8 +8327,11 @@
       <c r="L112" s="117" t="s">
         <v>809</v>
       </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M112" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="4" t="s">
         <v>442</v>
       </c>
@@ -8017,8 +8368,11 @@
       <c r="L113" s="117" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M113" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="4" t="s">
         <v>445</v>
       </c>
@@ -8055,8 +8409,11 @@
       <c r="L114" s="118" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M114" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="4" t="s">
         <v>448</v>
       </c>
@@ -8093,8 +8450,11 @@
       <c r="L115" s="117" t="s">
         <v>812</v>
       </c>
-    </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M115" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="4" t="s">
         <v>451</v>
       </c>
@@ -8131,8 +8491,11 @@
       <c r="L116" s="117" t="s">
         <v>813</v>
       </c>
-    </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M116" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="4" t="s">
         <v>356</v>
       </c>
@@ -8169,8 +8532,11 @@
       <c r="L117" s="117" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M117" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="4" t="s">
         <v>456</v>
       </c>
@@ -8207,8 +8573,11 @@
       <c r="L118" s="117" t="s">
         <v>815</v>
       </c>
-    </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M118" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="4" t="s">
         <v>370</v>
       </c>
@@ -8245,8 +8614,11 @@
       <c r="L119" s="119" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M119" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="4" t="s">
         <v>461</v>
       </c>
@@ -8283,8 +8655,11 @@
       <c r="L120" s="117" t="s">
         <v>818</v>
       </c>
-    </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M120" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="4" t="s">
         <v>464</v>
       </c>
@@ -8321,8 +8696,11 @@
       <c r="L121" s="117" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M121" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="8" t="s">
         <v>466</v>
       </c>
@@ -8359,8 +8737,11 @@
       <c r="L122" s="120" t="s">
         <v>820</v>
       </c>
-    </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M122" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="8" t="s">
         <v>469</v>
       </c>
@@ -8397,8 +8778,11 @@
       <c r="L123" s="120" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M123" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="50" t="s">
         <v>472</v>
       </c>
@@ -8433,8 +8817,11 @@
       <c r="L124" s="120" t="s">
         <v>822</v>
       </c>
-    </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M124" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="4" t="s">
         <v>474</v>
       </c>
@@ -8471,8 +8858,11 @@
       <c r="L125" s="122" t="s">
         <v>823</v>
       </c>
-    </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M125" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="4" t="s">
         <v>477</v>
       </c>
@@ -8509,8 +8899,11 @@
       <c r="L126" s="122" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M126" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="4" t="s">
         <v>480</v>
       </c>
@@ -8545,8 +8938,11 @@
       <c r="L127" s="122" t="s">
         <v>825</v>
       </c>
-    </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M127" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="4" t="s">
         <v>482</v>
       </c>
@@ -8581,8 +8977,11 @@
       <c r="L128" s="122" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="129" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="M128" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="15.6" x14ac:dyDescent="0.6">
       <c r="A129" s="55" t="s">
         <v>484</v>
       </c>
@@ -8619,8 +9018,11 @@
       <c r="L129" s="122" t="s">
         <v>827</v>
       </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M129" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="4" t="s">
         <v>487</v>
       </c>
@@ -8657,8 +9059,11 @@
       <c r="L130" s="123" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M130" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="4" t="s">
         <v>490</v>
       </c>
@@ -8695,8 +9100,11 @@
       <c r="L131" s="122" t="s">
         <v>829</v>
       </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M131" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="4" t="s">
         <v>493</v>
       </c>
@@ -8733,8 +9141,11 @@
       <c r="L132" s="122" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M132" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="4" t="s">
         <v>496</v>
       </c>
@@ -8769,8 +9180,11 @@
       <c r="L133" s="122" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M133" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="4" t="s">
         <v>498</v>
       </c>
@@ -8807,8 +9221,11 @@
       <c r="L134" s="122" t="s">
         <v>832</v>
       </c>
-    </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M134" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="4" t="s">
         <v>501</v>
       </c>
@@ -8845,8 +9262,11 @@
       <c r="L135" s="122" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M135" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="4" t="s">
         <v>504</v>
       </c>
@@ -8883,8 +9303,11 @@
       <c r="L136" s="122" t="s">
         <v>834</v>
       </c>
-    </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M136" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="4" t="s">
         <v>507</v>
       </c>
@@ -8921,8 +9344,11 @@
       <c r="L137" s="122" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M137" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="4" t="s">
         <v>510</v>
       </c>
@@ -8957,8 +9383,11 @@
       <c r="L138" s="122" t="s">
         <v>836</v>
       </c>
-    </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M138" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="4" t="s">
         <v>512</v>
       </c>
@@ -8995,8 +9424,11 @@
       <c r="L139" s="124" t="s">
         <v>837</v>
       </c>
-    </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M139" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="8" t="s">
         <v>515</v>
       </c>
@@ -9031,8 +9463,11 @@
       <c r="L140" s="125" t="s">
         <v>838</v>
       </c>
-    </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M140" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="8" t="s">
         <v>517</v>
       </c>
@@ -9069,8 +9504,11 @@
       <c r="L141" s="125" t="s">
         <v>839</v>
       </c>
-    </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M141" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="50" t="s">
         <v>520</v>
       </c>
@@ -9107,8 +9545,11 @@
       <c r="L142" s="126" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M142" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="50" t="s">
         <v>523</v>
       </c>
@@ -9145,8 +9586,11 @@
       <c r="L143" s="125" t="s">
         <v>841</v>
       </c>
-    </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M143" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="50" t="s">
         <v>526</v>
       </c>
@@ -9183,8 +9627,11 @@
       <c r="L144" s="125" t="s">
         <v>842</v>
       </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M144" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="50" t="s">
         <v>529</v>
       </c>
@@ -9221,8 +9668,11 @@
       <c r="L145" s="125" t="s">
         <v>843</v>
       </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M145" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="8" t="s">
         <v>381</v>
       </c>
@@ -9259,8 +9709,11 @@
       <c r="L146" s="127" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M146" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="8" t="s">
         <v>534</v>
       </c>
@@ -9297,8 +9750,11 @@
       <c r="L147" s="125" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M147" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="8" t="s">
         <v>537</v>
       </c>
@@ -9335,8 +9791,11 @@
       <c r="L148" s="125" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M148" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="8" t="s">
         <v>540</v>
       </c>
@@ -9373,8 +9832,11 @@
       <c r="L149" s="125" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M149" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="8" t="s">
         <v>543</v>
       </c>
@@ -9411,8 +9873,11 @@
       <c r="L150" s="125" t="s">
         <v>847</v>
       </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M150" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="8" t="s">
         <v>546</v>
       </c>
@@ -9447,8 +9912,11 @@
       <c r="L151" s="125" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M151" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="8" t="s">
         <v>548</v>
       </c>
@@ -9485,8 +9953,11 @@
       <c r="L152" s="125" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M152" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="8" t="s">
         <v>551</v>
       </c>
@@ -9523,8 +9994,11 @@
       <c r="L153" s="128" t="s">
         <v>849</v>
       </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M153" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="8" t="s">
         <v>554</v>
       </c>
@@ -9561,8 +10035,11 @@
       <c r="L154" s="125" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M154" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="8" t="s">
         <v>557</v>
       </c>
@@ -9597,8 +10074,11 @@
       <c r="L155" s="125" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M155" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="8" t="s">
         <v>402</v>
       </c>
@@ -9635,8 +10115,11 @@
       <c r="L156" s="125" t="s">
         <v>852</v>
       </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M156" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="8" t="s">
         <v>561</v>
       </c>
@@ -9673,8 +10156,11 @@
       <c r="L157" s="125" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M157" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="8" t="s">
         <v>564</v>
       </c>
@@ -9711,8 +10197,11 @@
       <c r="L158" s="125" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M158" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="8" t="s">
         <v>567</v>
       </c>
@@ -9749,8 +10238,11 @@
       <c r="L159" s="125" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M159" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="8" t="s">
         <v>570</v>
       </c>
@@ -9787,8 +10279,11 @@
       <c r="L160" s="125" t="s">
         <v>856</v>
       </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M160" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="8" t="s">
         <v>573</v>
       </c>
@@ -9825,8 +10320,11 @@
       <c r="L161" s="125" t="s">
         <v>857</v>
       </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M161" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="8" t="s">
         <v>576</v>
       </c>
@@ -9863,8 +10361,11 @@
       <c r="L162" s="125" t="s">
         <v>858</v>
       </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M162" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="8" t="s">
         <v>579</v>
       </c>
@@ -9899,8 +10400,11 @@
       <c r="L163" s="125" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M163" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="54" t="s">
         <v>861</v>
       </c>
@@ -9935,8 +10439,11 @@
       <c r="L164" s="122" t="s">
         <v>906</v>
       </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M164" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="54" t="s">
         <v>863</v>
       </c>
@@ -9973,8 +10480,11 @@
       <c r="L165" s="122" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M165" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="54" t="s">
         <v>370</v>
       </c>
@@ -10011,8 +10521,11 @@
       <c r="L166" s="122" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M166" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="4" t="s">
         <v>868</v>
       </c>
@@ -10049,8 +10562,11 @@
       <c r="L167" s="136" t="s">
         <v>909</v>
       </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M167" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="4" t="s">
         <v>871</v>
       </c>
@@ -10087,8 +10603,11 @@
       <c r="L168" s="136" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M168" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="4" t="s">
         <v>874</v>
       </c>
@@ -10123,8 +10642,11 @@
       <c r="L169" s="136" t="s">
         <v>911</v>
       </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M169" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="4" t="s">
         <v>876</v>
       </c>
@@ -10161,8 +10683,11 @@
       <c r="L170" s="136" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M170" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="4" t="s">
         <v>879</v>
       </c>
@@ -10199,8 +10724,11 @@
       <c r="L171" s="136" t="s">
         <v>913</v>
       </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M171" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="4" t="s">
         <v>882</v>
       </c>
@@ -10237,8 +10765,11 @@
       <c r="L172" s="136" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M172" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="4" t="s">
         <v>885</v>
       </c>
@@ -10275,8 +10806,11 @@
       <c r="L173" s="136" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="M173" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="4" t="s">
         <v>888</v>
       </c>
@@ -10313,8 +10847,16 @@
       <c r="L174" s="136" t="s">
         <v>916</v>
       </c>
+      <c r="M174" t="s">
+        <v>919</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="M2:M174">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"Pas de photo"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="L42" r:id="rId1" xr:uid="{8B70BA42-0B6F-4161-A27F-89B5B849A365}"/>
     <hyperlink ref="L28" r:id="rId2" xr:uid="{C33A62E6-F993-4CAD-9F72-602B25013CC7}"/>
